--- a/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第七章1.xlsx
+++ b/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第七章1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -266,7 +266,7 @@
     <t>医院下午</t>
   </si>
   <si>
-    <t>choice(进入第八章|loadScript(第八章,1000))</t>
+    <t>choice(进入第八章|loadScript(第八章1,1000))</t>
   </si>
   <si>
     <t>呜喵~</t>
@@ -2415,7 +2415,6 @@
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-      <c r="K54"/>
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
